--- a/src/assets/files/dkVstep/mau-phongthi.xlsx
+++ b/src/assets/files/dkVstep/mau-phongthi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\project\angular\v14\dangky-vstep\src\assets\files\dkVstep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C80BC0-2D4A-41A3-A470-D1E3B10FA264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44513A6E-FC38-4645-8F14-8A45D50C614B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8BF91288-6BA4-47E7-A5BF-CAE1DDE07FC4}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{8BF91288-6BA4-47E7-A5BF-CAE1DDE07FC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="17">
   <si>
     <t>STT</t>
   </si>
@@ -47,9 +47,6 @@
     <t xml:space="preserve">Phòng thi </t>
   </si>
   <si>
-    <t>Số lượng thí sinh</t>
-  </si>
-  <si>
     <t>Ngày thi</t>
   </si>
   <si>
@@ -80,10 +77,16 @@
     <t>Thời gian dự thi</t>
   </si>
   <si>
-    <t>13h30</t>
-  </si>
-  <si>
-    <t>06h30</t>
+    <t>Số lượng thí sinh Tối đa</t>
+  </si>
+  <si>
+    <t>Số lượng thí sinh dự thi</t>
+  </si>
+  <si>
+    <t>Sáng</t>
+  </si>
+  <si>
+    <t>Chiều</t>
   </si>
 </sst>
 </file>
@@ -113,20 +116,41 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -135,9 +159,6 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -149,6 +170,9 @@
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,315 +508,355 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77CE2848-B86C-49EE-935E-5C81C408F915}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" customWidth="1"/>
     <col min="6" max="6" width="19.28515625" customWidth="1"/>
     <col min="7" max="7" width="36.5703125" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2">
+        <v>40</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2">
+        <v>40</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>40</v>
+      </c>
+      <c r="E4" s="2">
+        <v>40</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2">
+        <v>40</v>
+      </c>
+      <c r="E5" s="2">
+        <v>40</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>40</v>
+      </c>
+      <c r="E6" s="2">
+        <v>40</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2">
+        <v>40</v>
+      </c>
+      <c r="E7" s="2">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="3">
-        <v>40</v>
-      </c>
-      <c r="E2" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="D8" s="2">
+        <v>40</v>
+      </c>
+      <c r="E8" s="2">
+        <v>40</v>
+      </c>
+      <c r="F8" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>40</v>
+      </c>
+      <c r="E9" s="2">
+        <v>40</v>
+      </c>
+      <c r="F9" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
+        <v>40</v>
+      </c>
+      <c r="E10" s="2">
+        <v>40</v>
+      </c>
+      <c r="F10" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2">
+        <v>40</v>
+      </c>
+      <c r="E11" s="2">
+        <v>40</v>
+      </c>
+      <c r="F11" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2">
+        <v>40</v>
+      </c>
+      <c r="E12" s="2">
+        <v>40</v>
+      </c>
+      <c r="F12" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
         <v>6</v>
       </c>
-      <c r="C3" s="3">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3">
-        <v>40</v>
-      </c>
-      <c r="E3" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
-        <v>40</v>
-      </c>
-      <c r="E4" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>40</v>
-      </c>
-      <c r="E5" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>40</v>
-      </c>
-      <c r="E6" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="D13" s="2">
+        <v>40</v>
+      </c>
+      <c r="E13" s="2">
+        <v>40</v>
+      </c>
+      <c r="F13" s="3">
+        <v>46047</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>40</v>
-      </c>
-      <c r="E7" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3">
-        <v>40</v>
-      </c>
-      <c r="E8" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2</v>
-      </c>
-      <c r="D9" s="3">
-        <v>40</v>
-      </c>
-      <c r="E9" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="3">
-        <v>3</v>
-      </c>
-      <c r="D10" s="3">
-        <v>40</v>
-      </c>
-      <c r="E10" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="3">
-        <v>4</v>
-      </c>
-      <c r="D11" s="3">
-        <v>40</v>
-      </c>
-      <c r="E11" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="3">
-        <v>5</v>
-      </c>
-      <c r="D12" s="3">
-        <v>40</v>
-      </c>
-      <c r="E12" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="3">
-        <v>6</v>
-      </c>
-      <c r="D13" s="3">
-        <v>40</v>
-      </c>
-      <c r="E13" s="4">
-        <v>46047</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
